--- a/output/pdf_financials_xlsx/HPM.xlsx
+++ b/output/pdf_financials_xlsx/HPM.xlsx
@@ -3126,19 +3126,19 @@
         <v>0.044784</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.080151</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.917717</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.303843</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.738166</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.63008</v>
       </c>
     </row>
     <row r="93">
@@ -4900,7 +4900,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -4949,7 +4953,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5406,7 +5414,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -5716,7 +5728,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HPM.xlsx
+++ b/output/pdf_financials_xlsx/HPM.xlsx
@@ -756,16 +756,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.016265</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006779</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003858</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.3e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1232,16 +1232,16 @@
         <v>-1.1742</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.441125</v>
+        <v>-5.45739</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.336537</v>
+        <v>-6.343316</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.509405</v>
+        <v>-1.513263</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.032054</v>
+        <v>-4.032077</v>
       </c>
     </row>
     <row r="28">
@@ -1292,16 +1292,16 @@
         <v>-1.1742</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.441125</v>
+        <v>-5.45739</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.336537</v>
+        <v>-6.343316</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.509405</v>
+        <v>-1.513263</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.032054</v>
+        <v>-4.032077</v>
       </c>
     </row>
     <row r="30">
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.276157</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.657907</v>
@@ -1447,10 +1447,10 @@
         <v>0.193957</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.176243</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.43132</v>
       </c>
     </row>
     <row r="35">
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.276157</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.657907</v>
@@ -1503,10 +1503,10 @@
         <v>0.193957</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.176243</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.43132</v>
       </c>
     </row>
     <row r="37">
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.279821</v>
+        <v>0.003664</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.083582</v>
@@ -1839,10 +1839,10 @@
         <v>0.060113</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.194977</v>
+        <v>0.018734</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.52935</v>
+        <v>0.09803000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
